--- a/MAJSushiConfig/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-immunization-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-immunization-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,7 +462,7 @@
     <t>author</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -567,7 +567,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -616,7 +616,7 @@
     <t>Immunization.extension:author.extension:actor.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-device-auteur-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-device-auteur-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0)
 </t>
   </si>
   <si>
@@ -626,7 +626,7 @@
     <t>Immunization.extension.url</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension</t>
   </si>
   <si>
     <t>Immunization.extension:author.value[x]</t>
@@ -675,7 +675,7 @@
     <t>Immunization.extension:basedOnRequestR5.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-request-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-request-document|0.1.0)
 </t>
   </si>
   <si>
@@ -876,7 +876,7 @@
     <t>cis</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-vaccine-code-cis|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-vaccine-code-cis|0.1.0</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding:translation</t>
@@ -885,7 +885,7 @@
     <t>translation</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-medication-translation-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-medication-translation-document|0.1.0</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding:translation.id</t>
@@ -1417,7 +1417,7 @@
     <t>Immunization.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1485,7 +1485,7 @@
     <t>Immunization.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-condition-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0)
 </t>
   </si>
   <si>
